--- a/seminars/qmsr-transition/QMSR-Gap-Assessment-Workbook.xlsx
+++ b/seminars/qmsr-transition/QMSR-Gap-Assessment-Workbook.xlsx
@@ -949,7 +949,7 @@
     <t xml:space="preserve">820.198(a)(3)</t>
   </si>
   <si>
-    <t xml:space="preserve">Y (all models)</t>
+    <t xml:space="preserve">Y (both models, except PMA preapproval)</t>
   </si>
   <si>
     <t xml:space="preserve">E-56</t>
@@ -979,7 +979,7 @@
     <t xml:space="preserve">820.65</t>
   </si>
   <si>
-    <t xml:space="preserve">Y (all models, where a tracking order applies)</t>
+    <t xml:space="preserve">Y (both models, where a tracking order was issued; except PMA preapproval)</t>
   </si>
   <si>
     <t xml:space="preserve">E-58</t>
@@ -1087,7 +1087,7 @@
     <t xml:space="preserve">Compliance Program 7382.850, Figure 2: Inspection Model 2 minimum elements</t>
   </si>
   <si>
-    <t xml:space="preserve">Model 2 applies to baseline surveillance inspections (no FDA inspection or MDSAP audit history, or risk factors indicating a need) and to PMA preapproval inspections. 22 elements, or 23 where the product is sterile. Model 1, used for every other inspection type, requires at least one element from each of the six QMS Areas plus all four OAFRs. Both models are minimums; FDA has said investigators routinely evaluate more.</t>
+    <t xml:space="preserve">Model 2 applies to baseline surveillance inspections (no FDA inspection or MDSAP audit history, or risk factors indicating a need) and to PMA preapproval inspections. 22 QMS Area elements, or 23 where the product is sterile. Model 1, used for every other inspection type, requires at least one element from each of the six QMS Areas plus the four OAFRs as applicable. Neither list is a ceiling: both figures instruct the investigator to consider additional elements where the inspection reveals objectionable conditions or the minimum coverage is not enough to assess something, and Figure 3 assigns most inspection types their model 'unless otherwise specified by the assignment'.</t>
   </si>
   <si>
     <t xml:space="preserve">Note</t>
@@ -1099,7 +1099,7 @@
     <t xml:space="preserve">For sterile product only</t>
   </si>
   <si>
-    <t xml:space="preserve">Other Applicable FDA Requirements (evaluated under both models)</t>
+    <t xml:space="preserve">Other Applicable FDA Requirements (both models on baseline surveillance; excluded on PMA preapproval)</t>
   </si>
   <si>
     <t xml:space="preserve">Evaluated in every risk-based inspection except PMA preapproval</t>
@@ -1111,7 +1111,7 @@
     <t xml:space="preserve">Reading the counts</t>
   </si>
   <si>
-    <t xml:space="preserve">23 QMS Area elements are listed, of which the sterile-product element applies only to sterile product: 23 for sterile product, 22 for non-sterile. The four OAFRs and the general items (registration and listing, marketing authorizations, previous 483 and compliance issues, and any areas defined in the assignment) are additional under both models.</t>
+    <t xml:space="preserve">23 QMS Area elements are listed, of which the sterile-product element applies only to sterile product: 23 for sterile product, 22 for non-sterile. The general items (registration and listing, marketing authorizations, previous 483 and compliance issues, and any areas defined in the assignment) are additional under both models. The four OAFRs are not: they are evaluated on a baseline surveillance inspection but excluded on a PMA preapproval inspection, which is Model 2's other use, and Medical Device Tracking is evaluated only where a tracking order was issued.</t>
   </si>
   <si>
     <t xml:space="preserve">Record content checklists: 21 CFR 820.35 and 820.45</t>
@@ -1999,7 +1999,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2102,10 +2102,6 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -6331,7 +6327,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
         <v>349</v>
       </c>
@@ -6634,17 +6630,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B38" s="26" t="s">
+      <c r="B38" s="20" t="s">
         <v>357</v>
       </c>
+      <c r="C38" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.5"/>
@@ -6699,7 +6697,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="26" t="s">
         <v>364</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -6710,7 +6708,7 @@
       <c r="E5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="27" t="s">
         <v>364</v>
       </c>
       <c r="B6" s="12" t="s">
@@ -6721,7 +6719,7 @@
       <c r="E6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="26" t="s">
         <v>367</v>
       </c>
       <c r="B7" s="10" t="s">
@@ -6732,7 +6730,7 @@
       <c r="E7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="27" t="s">
         <v>369</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -6743,7 +6741,7 @@
       <c r="E8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="26" t="s">
         <v>371</v>
       </c>
       <c r="B9" s="10" t="s">
@@ -6754,7 +6752,7 @@
       <c r="E9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="27" t="s">
         <v>373</v>
       </c>
       <c r="B10" s="12" t="s">
@@ -6765,7 +6763,7 @@
       <c r="E10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="26" t="s">
         <v>375</v>
       </c>
       <c r="B11" s="10" t="s">
@@ -6776,7 +6774,7 @@
       <c r="E11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="27" t="s">
         <v>377</v>
       </c>
       <c r="B12" s="12" t="s">
@@ -6787,7 +6785,7 @@
       <c r="E12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="26" t="s">
         <v>379</v>
       </c>
       <c r="B13" s="10" t="s">
@@ -6798,7 +6796,7 @@
       <c r="E13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="27" t="s">
         <v>381</v>
       </c>
       <c r="B14" s="12" t="s">
@@ -6809,7 +6807,7 @@
       <c r="E14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="26" t="s">
         <v>383</v>
       </c>
       <c r="B15" s="10" t="s">
@@ -6820,7 +6818,7 @@
       <c r="E15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="27" t="s">
         <v>385</v>
       </c>
       <c r="B16" s="12" t="s">
@@ -6831,7 +6829,7 @@
       <c r="E16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>387</v>
       </c>
       <c r="B17" s="10" t="s">
@@ -6842,7 +6840,7 @@
       <c r="E17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="27" t="s">
         <v>389</v>
       </c>
       <c r="B18" s="12" t="s">
@@ -6853,7 +6851,7 @@
       <c r="E18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="26" t="s">
         <v>391</v>
       </c>
       <c r="B19" s="10" t="s">
@@ -6864,7 +6862,7 @@
       <c r="E19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="27" t="s">
         <v>393</v>
       </c>
       <c r="B20" s="12" t="s">
@@ -6875,7 +6873,7 @@
       <c r="E20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="26" t="s">
         <v>395</v>
       </c>
       <c r="B21" s="10" t="s">
@@ -6886,7 +6884,7 @@
       <c r="E21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="27" t="s">
         <v>397</v>
       </c>
       <c r="B22" s="12" t="s">
@@ -6897,7 +6895,7 @@
       <c r="E22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="26" t="s">
         <v>399</v>
       </c>
       <c r="B23" s="10" t="s">
@@ -6908,7 +6906,7 @@
       <c r="E23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="27" t="s">
         <v>401</v>
       </c>
       <c r="B24" s="12" t="s">
@@ -6919,7 +6917,7 @@
       <c r="E24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="26" t="s">
         <v>403</v>
       </c>
       <c r="B25" s="10" t="s">
@@ -6930,7 +6928,7 @@
       <c r="E25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="27" t="s">
         <v>405</v>
       </c>
       <c r="B26" s="12" t="s">
@@ -6941,7 +6939,7 @@
       <c r="E26" s="7"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="26" t="s">
         <v>407</v>
       </c>
       <c r="B27" s="10" t="s">
@@ -6952,7 +6950,7 @@
       <c r="E27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="27" t="s">
         <v>409</v>
       </c>
       <c r="B28" s="12" t="s">
@@ -6963,7 +6961,7 @@
       <c r="E28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="26" t="s">
         <v>411</v>
       </c>
       <c r="B29" s="10" t="s">
@@ -6974,7 +6972,7 @@
       <c r="E29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="27" t="s">
         <v>413</v>
       </c>
       <c r="B30" s="12" t="s">
@@ -6985,7 +6983,7 @@
       <c r="E30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="26" t="s">
         <v>415</v>
       </c>
       <c r="B31" s="10" t="s">
@@ -6996,7 +6994,7 @@
       <c r="E31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="27" t="s">
         <v>415</v>
       </c>
       <c r="B32" s="12" t="s">
@@ -7007,28 +7005,28 @@
       <c r="E32" s="7"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="28" t="s">
         <v>418</v>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="28" t="n">
         <f aca="false">COUNTIF(C5:C32,"Y")</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="29" t="s">
+      <c r="B35" s="28" t="s">
         <v>419</v>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="28" t="n">
         <f aca="false">COUNTIF(C5:C32,"N")</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="29" t="s">
+      <c r="B36" s="28" t="s">
         <v>420</v>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="28" t="n">
         <f aca="false">28-COUNTIF(C5:C32,"Y")-COUNTIF(C5:C32,"N")-COUNTIF(C5:C32,"NA")</f>
         <v>28</v>
       </c>
@@ -7089,7 +7087,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="29" t="s">
         <v>426</v>
       </c>
       <c r="B5" s="23" t="s">
@@ -7103,7 +7101,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="30" t="s">
         <v>430</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -7117,7 +7115,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="29" t="s">
         <v>434</v>
       </c>
       <c r="B7" s="23" t="s">
@@ -7131,7 +7129,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="30" t="s">
         <v>436</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -7145,7 +7143,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="29" t="s">
         <v>438</v>
       </c>
       <c r="B9" s="23" t="s">
@@ -7159,7 +7157,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="30" t="s">
         <v>442</v>
       </c>
       <c r="B10" s="24" t="s">
@@ -7173,7 +7171,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="29" t="s">
         <v>446</v>
       </c>
       <c r="B11" s="23" t="s">
@@ -7187,7 +7185,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="30" t="s">
         <v>449</v>
       </c>
       <c r="B12" s="24" t="s">
@@ -7201,7 +7199,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="29" t="s">
         <v>452</v>
       </c>
       <c r="B13" s="23" t="s">
@@ -7215,7 +7213,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="30" t="s">
         <v>456</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -7229,7 +7227,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="29" t="s">
         <v>460</v>
       </c>
       <c r="B15" s="23" t="s">
@@ -7243,7 +7241,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="30" t="s">
         <v>462</v>
       </c>
       <c r="B16" s="24" t="s">
@@ -7257,7 +7255,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="29" t="s">
         <v>465</v>
       </c>
       <c r="B17" s="23" t="s">
@@ -7271,7 +7269,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="30" t="s">
         <v>468</v>
       </c>
       <c r="B18" s="24" t="s">
@@ -7285,7 +7283,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="29" t="s">
         <v>472</v>
       </c>
       <c r="B19" s="23" t="s">
@@ -7299,7 +7297,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="30" t="s">
         <v>475</v>
       </c>
       <c r="B20" s="24" t="s">
@@ -7313,7 +7311,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="29" t="s">
         <v>477</v>
       </c>
       <c r="B21" s="23" t="s">
@@ -7327,7 +7325,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="30" t="s">
         <v>481</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -7341,7 +7339,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="30" t="s">
+      <c r="A23" s="29" t="s">
         <v>484</v>
       </c>
       <c r="B23" s="23" t="s">
@@ -7355,7 +7353,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="30" t="s">
         <v>488</v>
       </c>
       <c r="B24" s="24" t="s">
@@ -7369,7 +7367,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="29" t="s">
         <v>490</v>
       </c>
       <c r="B25" s="23" t="s">
@@ -7383,7 +7381,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="30" t="s">
         <v>493</v>
       </c>
       <c r="B26" s="24" t="s">
@@ -7397,7 +7395,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="29" t="s">
         <v>496</v>
       </c>
       <c r="B27" s="23" t="s">
@@ -7411,7 +7409,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="30" t="s">
         <v>500</v>
       </c>
       <c r="B28" s="24" t="s">
@@ -7425,7 +7423,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="29" t="s">
         <v>504</v>
       </c>
       <c r="B29" s="23" t="s">
@@ -7502,10 +7500,10 @@
       <c r="A5" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="B5" s="32" t="n">
+      <c r="B5" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="33"/>
+      <c r="C5" s="32"/>
       <c r="D5" s="10" t="s">
         <v>515</v>
       </c>
@@ -7522,10 +7520,10 @@
       <c r="A6" s="12" t="s">
         <v>517</v>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="35"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="12" t="s">
         <v>518</v>
       </c>
@@ -7542,10 +7540,10 @@
       <c r="A7" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="B7" s="36" t="n">
+      <c r="B7" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="C7" s="35"/>
+      <c r="C7" s="34"/>
       <c r="D7" s="10" t="s">
         <v>518</v>
       </c>
@@ -7562,10 +7560,10 @@
       <c r="A8" s="12" t="s">
         <v>521</v>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="33"/>
+      <c r="C8" s="32"/>
       <c r="D8" s="12" t="s">
         <v>515</v>
       </c>
@@ -7582,10 +7580,10 @@
       <c r="A9" s="10" t="s">
         <v>523</v>
       </c>
-      <c r="B9" s="32" t="n">
+      <c r="B9" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="33"/>
+      <c r="C9" s="32"/>
       <c r="D9" s="10" t="s">
         <v>515</v>
       </c>
@@ -7602,10 +7600,10 @@
       <c r="A10" s="12" t="s">
         <v>525</v>
       </c>
-      <c r="B10" s="37" t="n">
+      <c r="B10" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="33"/>
+      <c r="C10" s="32"/>
       <c r="D10" s="12" t="s">
         <v>515</v>
       </c>
@@ -7622,10 +7620,10 @@
       <c r="A11" s="10" t="s">
         <v>527</v>
       </c>
-      <c r="B11" s="32" t="n">
+      <c r="B11" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="33"/>
+      <c r="C11" s="32"/>
       <c r="D11" s="10" t="s">
         <v>515</v>
       </c>
@@ -7642,10 +7640,10 @@
       <c r="A12" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="B12" s="37" t="n">
+      <c r="B12" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="33"/>
+      <c r="C12" s="32"/>
       <c r="D12" s="12" t="s">
         <v>515</v>
       </c>
@@ -7662,10 +7660,10 @@
       <c r="A13" s="10" t="s">
         <v>531</v>
       </c>
-      <c r="B13" s="32" t="n">
+      <c r="B13" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="33"/>
+      <c r="C13" s="32"/>
       <c r="D13" s="10" t="s">
         <v>515</v>
       </c>
@@ -7682,10 +7680,10 @@
       <c r="A14" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="B14" s="37" t="n">
+      <c r="B14" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="33"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="12" t="s">
         <v>515</v>
       </c>
@@ -7702,10 +7700,10 @@
       <c r="A15" s="10" t="s">
         <v>535</v>
       </c>
-      <c r="B15" s="32" t="n">
+      <c r="B15" s="31" t="n">
         <v>0.95</v>
       </c>
-      <c r="C15" s="33"/>
+      <c r="C15" s="32"/>
       <c r="D15" s="10" t="s">
         <v>515</v>
       </c>
@@ -7722,10 +7720,10 @@
       <c r="A16" s="12" t="s">
         <v>537</v>
       </c>
-      <c r="B16" s="37" t="n">
+      <c r="B16" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="33"/>
+      <c r="C16" s="32"/>
       <c r="D16" s="12" t="s">
         <v>515</v>
       </c>
@@ -7804,7 +7802,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="26" t="s">
         <v>546</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -7824,7 +7822,7 @@
       <c r="H5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="27" t="s">
         <v>551</v>
       </c>
       <c r="B6" s="12" t="s">
@@ -7844,7 +7842,7 @@
       <c r="H6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="26" t="s">
         <v>556</v>
       </c>
       <c r="B7" s="10" t="s">
@@ -7864,7 +7862,7 @@
       <c r="H7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="27" t="s">
         <v>561</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -7884,7 +7882,7 @@
       <c r="H8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="26" t="s">
         <v>566</v>
       </c>
       <c r="B9" s="10" t="s">
@@ -7904,7 +7902,7 @@
       <c r="H9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="27" t="s">
         <v>571</v>
       </c>
       <c r="B10" s="12" t="s">
